--- a/data/raw/sales/Week 24/Tonor/Vendor Sales (SP-API).xlsx
+++ b/data/raw/sales/Week 24/Tonor/Vendor Sales (SP-API).xlsx
@@ -549,7 +549,7 @@
         <v>25515.08</v>
       </c>
       <c r="J2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -681,13 +681,13 @@
         <v>18298.27</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -741,19 +741,19 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5082.2</v>
+        <v>6776.27</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -939,13 +939,13 @@
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>20499.16</v>
+        <v>24226.28</v>
       </c>
       <c r="J8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1005,13 +1005,13 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10166.12</v>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>7624.59</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1137,13 +1137,13 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>23716.95</v>
+        <v>28799.14</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
         <v>17197.46</v>
       </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1401,13 +1401,13 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>6776.28</v>
+        <v>8470.35</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
